--- a/translators/xlsx/tests/sample_numfmt.xlsx
+++ b/translators/xlsx/tests/sample_numfmt.xlsx
@@ -15,7 +15,6 @@
   </numFmts>
   <fonts count="1">
     <font>
-      <sz val="11"/>
       <name val="Calibri"/>
     </font>
   </fonts>
